--- a/artfynd/Lill-Smaltjärnen artfynd.xlsx
+++ b/artfynd/Lill-Smaltjärnen artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2018789</v>
+        <v>1759908</v>
       </c>
       <c r="B2" t="n">
-        <v>80119</v>
+        <v>93235</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6464</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>674598</v>
+        <v>674677</v>
       </c>
       <c r="R2" t="n">
-        <v>7144476</v>
+        <v>7144413</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,7 +760,7 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sveaskog Västerbotten</t>
+          <t>Daniella Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -779,11 +779,11 @@
         <v>1854363</v>
       </c>
       <c r="B3" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -861,7 +861,7 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sveaskog Västerbotten</t>
+          <t>Daniella Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -880,7 +880,7 @@
         <v>1975829</v>
       </c>
       <c r="B4" t="n">
-        <v>80083</v>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Sveaskog Västerbotten</t>
+          <t>Daniella Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -978,32 +978,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1759908</v>
+        <v>2018789</v>
       </c>
       <c r="B5" t="n">
-        <v>92571</v>
+        <v>80468</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>6464</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>674677</v>
+        <v>674598</v>
       </c>
       <c r="R5" t="n">
-        <v>7144413</v>
+        <v>7144476</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,7 +1063,7 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Sveaskog Västerbotten</t>
+          <t>Daniella Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
